--- a/data/trans_dic/P62A$invalidez-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P62A$invalidez-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de invalidez</t>
+          <t>Población que, al menos, percibe una pensión de invalidez (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 20,07</t>
+          <t>5,35; 20,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 24,29</t>
+          <t>5,85; 22,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 13,96</t>
+          <t>3,03; 14,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 20,98</t>
+          <t>2,4; 20,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 26,52</t>
+          <t>4,92; 27,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 15,78</t>
+          <t>1,8; 16,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 12,91</t>
+          <t>2,5; 12,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 17,1</t>
+          <t>5,43; 16,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,4; 21,74</t>
+          <t>7,54; 22,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 11,54</t>
+          <t>3,31; 12,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,8</t>
+          <t>0,98; 4,68</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,26</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,57; 23,66</t>
+          <t>6,68; 24,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 18,1</t>
+          <t>4,26; 17,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,98</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 36,35</t>
+          <t>3,47; 35,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,13; 41,69</t>
+          <t>7,99; 42,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 26,0</t>
+          <t>2,76; 25,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 17,55</t>
+          <t>5,69; 17,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 11,63</t>
+          <t>1,92; 11,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,74; 24,92</t>
+          <t>9,37; 24,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 16,92</t>
+          <t>5,29; 17,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,77</t>
+          <t>2,54; 7,26</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 19,08</t>
+          <t>7,56; 20,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,17; 21,59</t>
+          <t>9,78; 21,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,45</t>
+          <t>3,04; 11,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 32,58</t>
+          <t>3,85; 32,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 23,48</t>
+          <t>5,48; 25,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 16,59</t>
+          <t>1,9; 16,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,17; 33,92</t>
+          <t>17,18; 34,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 19,56</t>
+          <t>7,64; 18,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 19,8</t>
+          <t>10,16; 19,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 10,46</t>
+          <t>3,66; 9,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 10,91</t>
+          <t>5,29; 11,07</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 10,14</t>
+          <t>4,98; 10,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,66; 22,54</t>
+          <t>14,44; 22,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 15,11</t>
+          <t>7,91; 14,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,67</t>
+          <t>0,67; 3,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,64; 20,54</t>
+          <t>7,6; 20,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 19,66</t>
+          <t>6,4; 19,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 17,38</t>
+          <t>6,67; 17,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 20,2</t>
+          <t>1,93; 20,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 10,97</t>
+          <t>6,21; 11,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,08; 20,45</t>
+          <t>13,33; 20,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 14,75</t>
+          <t>7,99; 14,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,59</t>
+          <t>1,73; 7,49</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,82; 23,33</t>
+          <t>7,34; 23,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 19,69</t>
+          <t>8,65; 19,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 13,73</t>
+          <t>5,44; 13,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,13</t>
+          <t>0,38; 5,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,01; 18,53</t>
+          <t>6,16; 19,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,83; 19,62</t>
+          <t>9,79; 18,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,6; 15,11</t>
+          <t>6,69; 15,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,12; 41,14</t>
+          <t>32,42; 41,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,0; 18,37</t>
+          <t>8,35; 18,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,42; 17,68</t>
+          <t>10,61; 17,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,08; 13,18</t>
+          <t>7,15; 13,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,22; 26,53</t>
+          <t>20,45; 26,59</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,55; 92,56</t>
+          <t>41,56; 92,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,8; 87,7</t>
+          <t>33,9; 87,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,23; 100,0</t>
+          <t>38,41; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,29</t>
+          <t>2,47; 7,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,68; 8,0</t>
+          <t>2,68; 8,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,4</t>
+          <t>0,81; 4,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>76,71; 85,5</t>
+          <t>76,35; 85,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,17</t>
+          <t>4,21; 10,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,3; 12,06</t>
+          <t>5,02; 12,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,99</t>
+          <t>2,57; 7,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71,79; 80,8</t>
+          <t>71,79; 81,3</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,64; 12,22</t>
+          <t>7,68; 12,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,63; 19,1</t>
+          <t>13,69; 19,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,87; 12,03</t>
+          <t>7,93; 11,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,43</t>
+          <t>0,8; 2,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,58</t>
+          <t>6,11; 10,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,33; 13,03</t>
+          <t>8,24; 12,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,53</t>
+          <t>5,6; 9,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,58; 40,79</t>
+          <t>16,11; 40,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,64; 10,82</t>
+          <t>7,59; 10,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,99; 15,56</t>
+          <t>11,99; 15,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,24</t>
+          <t>7,27; 10,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,84; 20,25</t>
+          <t>11,46; 20,28</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de invalidez</t>
+          <t>Población que, al menos, percibe una pensión de invalidez (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4732; 17471</t>
+          <t>4659; 18057</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4264; 17014</t>
+          <t>4101; 16095</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3083; 13707</t>
+          <t>2970; 14221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1282</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1019; 8748</t>
+          <t>1001; 8733</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1868; 9875</t>
+          <t>1831; 10141</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>912; 7831</t>
+          <t>894; 7965</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1799; 8288</t>
+          <t>1608; 7821</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7327; 22011</t>
+          <t>6996; 21343</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7936; 23326</t>
+          <t>8093; 24075</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5135; 17059</t>
+          <t>4899; 17847</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1378; 8062</t>
+          <t>1642; 7855</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6282</t>
+          <t>0; 5984</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6263; 22569</t>
+          <t>6377; 23336</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3123; 14333</t>
+          <t>3374; 13831</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5366</t>
+          <t>0; 5012</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>950; 9399</t>
+          <t>896; 9191</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2289; 15564</t>
+          <t>2982; 15984</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1080; 9461</t>
+          <t>1003; 9347</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3427; 10595</t>
+          <t>3433; 10354</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1838; 11853</t>
+          <t>1959; 12093</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11606; 33072</t>
+          <t>12435; 32428</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6092; 19549</t>
+          <t>6111; 19865</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4274; 13061</t>
+          <t>4266; 12210</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9465; 22580</t>
+          <t>8943; 23683</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18829; 39964</t>
+          <t>18095; 39293</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6293; 19890</t>
+          <t>5277; 19809</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4133</t>
+          <t>0; 4325</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>801; 6917</t>
+          <t>817; 6845</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2268; 13838</t>
+          <t>3226; 15118</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>915; 8142</t>
+          <t>933; 8071</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8865; 17511</t>
+          <t>8870; 17922</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10998; 27304</t>
+          <t>10663; 26266</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24701; 48310</t>
+          <t>24794; 47675</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8222; 23302</t>
+          <t>8166; 22050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9569; 19934</t>
+          <t>9665; 20227</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17176; 36677</t>
+          <t>18010; 37029</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47770; 78839</t>
+          <t>50503; 79813</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26721; 52237</t>
+          <t>27342; 51674</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1820; 10842</t>
+          <t>1968; 10974</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8633; 23208</t>
+          <t>8586; 22822</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7421; 22774</t>
+          <t>7409; 23133</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9719; 25127</t>
+          <t>9640; 25989</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5318; 66944</t>
+          <t>6394; 68107</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29220; 52078</t>
+          <t>29499; 54391</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60919; 95234</t>
+          <t>62074; 95569</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40244; 72300</t>
+          <t>39186; 70540</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11745; 47543</t>
+          <t>10814; 46949</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6467; 19298</t>
+          <t>6067; 19780</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12592; 30069</t>
+          <t>13201; 29616</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10833; 26599</t>
+          <t>10535; 27012</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>913; 8652</t>
+          <t>542; 8198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6077; 18745</t>
+          <t>6229; 19919</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22266; 44448</t>
+          <t>22185; 42897</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13616; 31160</t>
+          <t>13786; 31059</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>71126; 91111</t>
+          <t>71800; 91993</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14713; 33772</t>
+          <t>15344; 33897</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39516; 67034</t>
+          <t>40232; 67590</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28312; 52692</t>
+          <t>28610; 52550</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>73315; 96195</t>
+          <t>74124; 96403</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4174; 9528</t>
+          <t>4278; 9513</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5440; 14115</t>
+          <t>5456; 14011</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3228; 8443</t>
+          <t>3243; 8443</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1574</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5936; 19902</t>
+          <t>6748; 19817</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7221; 21533</t>
+          <t>7210; 21924</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2079; 13435</t>
+          <t>2003; 11913</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>150431; 167677</t>
+          <t>149730; 167157</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12431; 28828</t>
+          <t>11939; 29379</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15109; 34395</t>
+          <t>14324; 34843</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6728; 20539</t>
+          <t>6606; 20154</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>148566; 167228</t>
+          <t>148574; 168253</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>56256; 89910</t>
+          <t>56548; 88777</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118503; 166034</t>
+          <t>119005; 165409</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>70784; 108104</t>
+          <t>71270; 107766</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6288; 19225</t>
+          <t>6313; 18626</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>34552; 60976</t>
+          <t>35221; 63012</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62068; 97117</t>
+          <t>61421; 96375</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39642; 70008</t>
+          <t>41136; 70450</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>153400; 377409</t>
+          <t>149012; 377029</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>100204; 141956</t>
+          <t>99617; 142612</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>193488; 251188</t>
+          <t>193482; 255631</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>117631; 167333</t>
+          <t>118724; 165274</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>202960; 347238</t>
+          <t>196518; 347774</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$invalidez-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P62A$invalidez-Clase-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 20,74</t>
+          <t>5,44; 19,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 22,98</t>
+          <t>6,03; 24,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 14,49</t>
+          <t>3,16; 14,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 20,95</t>
+          <t>2,42; 20,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 27,23</t>
+          <t>4,94; 26,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 16,05</t>
+          <t>1,8; 14,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 12,18</t>
+          <t>2,41; 12,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,43; 16,58</t>
+          <t>5,73; 17,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,54; 22,44</t>
+          <t>7,49; 21,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 12,07</t>
+          <t>3,36; 11,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,68</t>
+          <t>0,82; 4,64</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,0; 7,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,68; 24,46</t>
+          <t>6,51; 23,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 17,47</t>
+          <t>4,39; 18,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 35,54</t>
+          <t>3,49; 35,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,99; 42,82</t>
+          <t>7,75; 43,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 25,69</t>
+          <t>2,77; 25,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,69; 17,15</t>
+          <t>5,6; 16,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,87</t>
+          <t>1,77; 11,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,37; 24,43</t>
+          <t>8,98; 23,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 17,19</t>
+          <t>5,25; 16,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,26</t>
+          <t>2,6; 7,45</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 20,01</t>
+          <t>7,51; 20,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,78; 21,23</t>
+          <t>10,12; 21,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 11,4</t>
+          <t>3,55; 11,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,3</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 32,25</t>
+          <t>3,81; 33,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 25,66</t>
+          <t>5,33; 25,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 16,45</t>
+          <t>1,8; 15,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,18; 34,71</t>
+          <t>16,35; 35,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 18,82</t>
+          <t>8,0; 18,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,16; 19,54</t>
+          <t>10,15; 19,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,89</t>
+          <t>3,67; 11,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 11,07</t>
+          <t>5,28; 11,18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,24</t>
+          <t>4,85; 10,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,44; 22,82</t>
+          <t>13,97; 22,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 14,95</t>
+          <t>7,71; 15,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,72</t>
+          <t>0,61; 3,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,6; 20,19</t>
+          <t>7,57; 20,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 19,97</t>
+          <t>6,88; 20,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 17,98</t>
+          <t>7,0; 17,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 20,55</t>
+          <t>13,43; 24,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,46</t>
+          <t>6,26; 11,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,33; 20,52</t>
+          <t>13,07; 20,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,99; 14,39</t>
+          <t>8,03; 14,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,49</t>
+          <t>4,91; 8,81</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,34; 23,92</t>
+          <t>7,78; 24,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 19,4</t>
+          <t>8,32; 19,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,44; 13,95</t>
+          <t>5,75; 14,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,81</t>
+          <t>0,61; 5,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 19,69</t>
+          <t>6,0; 18,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,79; 18,93</t>
+          <t>9,52; 19,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,69; 15,06</t>
+          <t>6,53; 15,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,42; 41,54</t>
+          <t>31,61; 41,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,35; 18,44</t>
+          <t>8,28; 18,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,61; 17,82</t>
+          <t>10,34; 17,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,15; 13,14</t>
+          <t>7,2; 13,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,45; 26,59</t>
+          <t>19,98; 26,46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,54%</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,56; 92,41</t>
+          <t>42,41; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,9; 87,05</t>
+          <t>33,66; 86,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,41; 100,0</t>
+          <t>38,14; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,26</t>
+          <t>2,29; 7,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,68; 8,14</t>
+          <t>2,63; 8,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,79</t>
+          <t>0,82; 5,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>76,35; 85,24</t>
+          <t>76,6; 85,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,21; 10,37</t>
+          <t>4,1; 10,31</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,02; 12,21</t>
+          <t>5,28; 11,9</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,84</t>
+          <t>2,52; 8,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71,79; 81,3</t>
+          <t>72,75; 82,02</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,68; 12,06</t>
+          <t>7,62; 12,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,69; 19,03</t>
+          <t>13,74; 19,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,93; 11,99</t>
+          <t>7,96; 12,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,36</t>
+          <t>0,75; 2,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,94</t>
+          <t>6,18; 10,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,24; 12,93</t>
+          <t>8,39; 13,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,6; 9,59</t>
+          <t>5,51; 9,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,11; 40,75</t>
+          <t>36,66; 41,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,59; 10,87</t>
+          <t>7,6; 10,75</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,99; 15,84</t>
+          <t>12,1; 15,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 10,12</t>
+          <t>7,4; 10,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,46; 20,28</t>
+          <t>18,05; 21,08</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4478</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4478</t>
         </is>
       </c>
     </row>
@@ -1927,17 +1927,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4659; 18057</t>
+          <t>4735; 16998</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4101; 16095</t>
+          <t>4221; 16862</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2970; 14221</t>
+          <t>3102; 14463</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1947,42 +1947,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1001; 8733</t>
+          <t>1011; 8660</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1831; 10141</t>
+          <t>1839; 9854</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>894; 7965</t>
+          <t>895; 7413</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1608; 7821</t>
+          <t>1752; 9162</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6996; 21343</t>
+          <t>7374; 22181</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8093; 24075</t>
+          <t>8038; 22935</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4899; 17847</t>
+          <t>4960; 16707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1642; 7855</t>
+          <t>1562; 8786</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>8398</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5984</t>
+          <t>0; 6055</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6377; 23336</t>
+          <t>6210; 22306</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3374; 13831</t>
+          <t>3479; 14534</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5012</t>
+          <t>0; 5336</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>896; 9191</t>
+          <t>903; 9157</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2982; 15984</t>
+          <t>2894; 16175</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1003; 9347</t>
+          <t>1009; 9360</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3433; 10354</t>
+          <t>3845; 11421</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1959; 12093</t>
+          <t>1802; 12197</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12435; 32428</t>
+          <t>11925; 31597</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6111; 19865</t>
+          <t>6068; 18609</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4266; 12210</t>
+          <t>4824; 13815</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>15689</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8943; 23683</t>
+          <t>8892; 23690</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18095; 39293</t>
+          <t>18722; 39026</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5277; 19809</t>
+          <t>6171; 19790</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4325</t>
+          <t>0; 4230</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>817; 6845</t>
+          <t>809; 7125</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3226; 15118</t>
+          <t>3141; 14989</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>933; 8071</t>
+          <t>884; 7666</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8870; 17922</t>
+          <t>9271; 20293</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10663; 26266</t>
+          <t>11161; 26476</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24794; 47675</t>
+          <t>24770; 48049</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8166; 22050</t>
+          <t>8187; 24850</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9665; 20227</t>
+          <t>10573; 22364</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28799</t>
+          <t>30336</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18010; 37029</t>
+          <t>17522; 36850</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50503; 79813</t>
+          <t>48870; 79367</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27342; 51674</t>
+          <t>26666; 52795</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1968; 10974</t>
+          <t>1956; 11901</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8586; 22822</t>
+          <t>8555; 23443</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7409; 23133</t>
+          <t>7973; 23541</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9640; 25989</t>
+          <t>10124; 26000</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6394; 68107</t>
+          <t>18483; 33387</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29499; 54391</t>
+          <t>29720; 52663</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62074; 95569</t>
+          <t>60879; 95837</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39186; 70540</t>
+          <t>39394; 69353</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10814; 46949</t>
+          <t>22552; 40434</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>81320</t>
+          <t>87505</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84508</t>
+          <t>90859</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6067; 19780</t>
+          <t>6434; 20226</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13201; 29616</t>
+          <t>12698; 30175</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10535; 27012</t>
+          <t>11135; 27118</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>542; 8198</t>
+          <t>921; 8939</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6229; 19919</t>
+          <t>6071; 18810</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22185; 42897</t>
+          <t>21565; 43234</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13786; 31059</t>
+          <t>13473; 32198</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>71800; 91993</t>
+          <t>76607; 99586</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15344; 33897</t>
+          <t>15221; 33329</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40232; 67590</t>
+          <t>39216; 67047</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28610; 52550</t>
+          <t>28787; 53232</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>74124; 96403</t>
+          <t>78597; 104071</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>159411</t>
+          <t>171998</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>159411</t>
+          <t>171998</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4278; 9513</t>
+          <t>4366; 10294</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5456; 14011</t>
+          <t>5418; 13991</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3243; 8443</t>
+          <t>3220; 8443</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6748; 19817</t>
+          <t>6259; 19988</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7210; 21924</t>
+          <t>7090; 23006</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2003; 11913</t>
+          <t>2027; 12796</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>149730; 167157</t>
+          <t>161922; 180069</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11939; 29379</t>
+          <t>11610; 29212</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14324; 34843</t>
+          <t>15068; 33966</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6606; 20154</t>
+          <t>6469; 21569</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>148574; 168253</t>
+          <t>161366; 181931</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>287339</t>
+          <t>310118</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>298487</t>
+          <t>321759</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>56548; 88777</t>
+          <t>56108; 89692</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>119005; 165409</t>
+          <t>119438; 167404</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>71270; 107766</t>
+          <t>71578; 109833</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6313; 18626</t>
+          <t>6490; 19147</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>35221; 63012</t>
+          <t>35608; 60881</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>61421; 96375</t>
+          <t>62522; 97020</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41136; 70450</t>
+          <t>40509; 72175</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>149012; 377029</t>
+          <t>289329; 330124</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>99617; 142612</t>
+          <t>99676; 141076</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>193482; 255631</t>
+          <t>195386; 253910</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>118724; 165274</t>
+          <t>120854; 167753</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>196518; 347774</t>
+          <t>297684; 347625</t>
         </is>
       </c>
     </row>
